--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -33837,6 +33837,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -33860,6 +33860,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -33906,6 +33906,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -33770,22 +33770,22 @@
     </row>
     <row r="1453">
       <c r="A1453" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1453" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="C1453" t="n">
-        <v>0.800000011920929</v>
+        <v>0.785000026226044</v>
       </c>
       <c r="D1453" t="n">
-        <v>0.800000011920929</v>
+        <v>0.785000026226044</v>
       </c>
       <c r="E1453" t="n">
-        <v>0.800000011920929</v>
+        <v>0.785000026226044</v>
       </c>
       <c r="F1453" t="n">
-        <v>0.800000011920929</v>
+        <v>0.785000026226044</v>
       </c>
       <c r="G1453" t="s">
         <v>7</v>
@@ -33793,10 +33793,10 @@
     </row>
     <row r="1454">
       <c r="A1454" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1454" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="C1454" t="n">
         <v>0.800000011920929</v>
@@ -33816,22 +33816,22 @@
     </row>
     <row r="1455">
       <c r="A1455" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1455" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="C1455" t="n">
-        <v>0.810000002384186</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="D1455" t="n">
-        <v>0.810000002384186</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="E1455" t="n">
-        <v>0.810000002384186</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="F1455" t="n">
-        <v>0.810000002384186</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="G1455" t="s">
         <v>7</v>
@@ -33839,10 +33839,10 @@
     </row>
     <row r="1456">
       <c r="A1456" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1456" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="C1456" t="n">
         <v>0.810000002384186</v>
@@ -33862,7 +33862,7 @@
     </row>
     <row r="1457">
       <c r="A1457" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1457" t="n">
         <v>0</v>
@@ -33885,10 +33885,10 @@
     </row>
     <row r="1458">
       <c r="A1458" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1458" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="C1458" t="n">
         <v>0.810000002384186</v>
@@ -33908,10 +33908,10 @@
     </row>
     <row r="1459">
       <c r="A1459" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1459" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="C1459" t="n">
         <v>0.810000002384186</v>
@@ -33926,6 +33926,52 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1459" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>0.810000002384186</v>
+      </c>
+      <c r="G1460" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>700</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>0.774999976158142</v>
+      </c>
+      <c r="G1461" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -38465,6 +38465,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="H1466" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -38491,6 +38491,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>19600</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="H1467" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -38569,6 +38569,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>20300</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="H1470" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -34244,8 +34244,31 @@
       <c r="E1473" t="n">
         <v>0.555000007152557</v>
       </c>
-      <c r="F1473"/>
+      <c r="F1473" t="n">
+        <v>0.540000021457672</v>
+      </c>
       <c r="G1473" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>32200</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="F1474"/>
+      <c r="G1474" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -34267,8 +34267,31 @@
       <c r="E1474" t="n">
         <v>0.540000021457672</v>
       </c>
-      <c r="F1474"/>
+      <c r="F1474" t="n">
+        <v>0.550000011920929</v>
+      </c>
       <c r="G1474" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>18900</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>0.509999990463257</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="F1475"/>
+      <c r="G1475" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -34290,8 +34290,31 @@
       <c r="E1475" t="n">
         <v>0.529999971389771</v>
       </c>
-      <c r="F1475"/>
+      <c r="F1475" t="n">
+        <v>0.540000021457672</v>
+      </c>
       <c r="G1475" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1476" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F1476"/>
+      <c r="G1476" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -34313,8 +34313,31 @@
       <c r="E1476" t="n">
         <v>0.524999976158142</v>
       </c>
-      <c r="F1476"/>
+      <c r="F1476" t="n">
+        <v>0.524999976158142</v>
+      </c>
       <c r="G1476" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1477" t="n">
+        <v>18900</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>0.490000009536743</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>0.514999985694885</v>
+      </c>
+      <c r="F1477"/>
+      <c r="G1477" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -34343,6 +34343,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1478">
+      <c r="A1478" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1478" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>0.495999991893768</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>0.48199999332428</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="G1478" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -38855,6 +38855,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1481" t="n">
+        <v>27300</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>0.535000026226044</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="H1481" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -38881,6 +38881,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1482">
+      <c r="A1482" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1482" t="n">
+        <v>11900</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>0.555000007152557</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>0.529999971389771</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1482" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43356,6 +43356,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1483">
+      <c r="A1483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1483" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1484" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I1484" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43414,6 +43414,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1485">
+      <c r="A1485" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1485" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1485" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H1485" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1485" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43443,6 +43443,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1486">
+      <c r="A1486" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1486" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1486" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1486" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1486" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43472,6 +43472,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1487">
+      <c r="A1487" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1487" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1487" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1487" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H1487" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1487" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43501,6 +43501,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1488">
+      <c r="A1488" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1488" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1488" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="G1488" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="H1488" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1489" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>0.545000016689301</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1489" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1489" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I1489" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43559,6 +43559,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1490">
+      <c r="A1490" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1490" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1490" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1490" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1490" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TNX.MI.xlsx
+++ b/data/TNX.MI.xlsx
@@ -43588,6 +43588,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1491" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1491" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G1491" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="H1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1491" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
